--- a/excel/15数学函数与Row.xlsx
+++ b/excel/15数学函数与Row.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435D82AE-AFF8-5A4A-8704-5D9F12EC4E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EDF4F-7190-224F-9BFF-E687DFC8C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,6 +301,76 @@
   </si>
   <si>
     <t>F9刷新图表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王五</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵六</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XM-20100003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XM-20100004</t>
+  </si>
+  <si>
+    <t>XM-20100005</t>
+  </si>
+  <si>
+    <t>XM-20100006</t>
+  </si>
+  <si>
+    <t>XM-20100007</t>
+  </si>
+  <si>
+    <t>XM-20100008</t>
+  </si>
+  <si>
+    <t>XM-20100009</t>
+  </si>
+  <si>
+    <t>张三的订单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、SMALL函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMALL(array,k)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1需要找到第 k 个最小值的数组或数值数据区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2要返回的数据在数组或数据区域里的位置（从小到大）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LARGE(array,k)与SMALL相反 取最大值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -311,7 +381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -374,6 +444,13 @@
     <font>
       <sz val="10"/>
       <color theme="3" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -470,7 +547,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -523,6 +600,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -897,7 +977,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:H30"/>
+  <dimension ref="A2:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -991,66 +1071,75 @@
     </row>
     <row r="16" spans="1:8" s="3" customFormat="1" ht="14"/>
     <row r="17" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="B17" s="7"/>
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="14"/>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="B19" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="C18" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" s="3" customFormat="1">
+      <c r="C19" s="4"/>
+      <c r="G19" s="6"/>
+    </row>
     <row r="20" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C20" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" s="3" customFormat="1">
-      <c r="C21" s="4"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="B22" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C23" s="17" t="s">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="C21" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F21" s="17">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>91</v>
-      </c>
-      <c r="G23" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="2:7" s="3" customFormat="1" ht="14"/>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="14"/>
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="C24" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
     <row r="25" spans="2:7">
-      <c r="C25" s="3"/>
+      <c r="C25" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="C26" s="3"/>
+      <c r="C26" s="21" t="s">
+        <v>87</v>
+      </c>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="2:7">
+      <c r="C27" s="21" t="s">
+        <v>88</v>
+      </c>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="2:7">
       <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="E30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1249,16 +1338,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:14">
       <c r="A1" s="18" t="s">
         <v>43</v>
       </c>
@@ -1266,8 +1357,17 @@
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
       <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="K1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1384,18 @@
         <v>18982.847759558852</v>
       </c>
       <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="K2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="8" t="str" cm="1">
+        <f t="array" ref="N2">INDEX(L:L,SMALL(IF(K$2:$K8="张三",ROW($2:$8),2^20),ROW(1:1)))&amp;""</f>
+        <v>XM-20100003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1306,8 +1416,18 @@
         <v>49</v>
       </c>
       <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="K3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="8" t="str" cm="1">
+        <f t="array" ref="N3">INDEX(L:L,SMALL(IF(K$2:$K9="张三",ROW($2:$8),2^20),ROW(2:2)))&amp;""</f>
+        <v>XM-20100006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
@@ -1329,8 +1449,18 @@
         <v>40893.083149311875</v>
       </c>
       <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="K4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" s="8" t="str" cm="1">
+        <f t="array" ref="N4">INDEX(L:L,SMALL(IF(K$2:$K10="张三",ROW($2:$8),2^20),ROW(3:3)))&amp;""</f>
+        <v>XM-20100009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1482,18 @@
         <v>43537.557757683368</v>
       </c>
       <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="K5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="8" t="str" cm="1">
+        <f t="array" ref="N5">INDEX(L:L,SMALL(IF(K$2:$K11="张三",ROW($2:$8),2^20),ROW(4:4)))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="18" t="s">
         <v>44</v>
       </c>
@@ -1367,8 +1507,14 @@
         <v>51700.030820578511</v>
       </c>
       <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="K6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="10" t="s">
         <v>3</v>
       </c>
@@ -1390,8 +1536,14 @@
         <v>32726.657776180989</v>
       </c>
       <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="K7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="10" t="s">
         <v>3</v>
       </c>
@@ -1413,8 +1565,14 @@
         <v>43537.557757683368</v>
       </c>
       <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="K8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="10" t="s">
         <v>3</v>
       </c>
@@ -1433,7 +1591,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:14">
       <c r="A10" s="10" t="s">
         <v>3</v>
       </c>
@@ -1450,7 +1608,7 @@
         <v>44258.364560249865</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:14">
       <c r="A11" s="18" t="s">
         <v>45</v>
       </c>
@@ -1459,7 +1617,7 @@
       <c r="D11" s="19"/>
       <c r="E11" s="20"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:14">
       <c r="A12" s="10" t="s">
         <v>3</v>
       </c>
@@ -1476,7 +1634,7 @@
         <v>92391.153643258687</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:14">
       <c r="A13" s="10" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1651,7 @@
         <v>51700.030820578511</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:14">
       <c r="A14" s="10" t="s">
         <v>3</v>
       </c>
@@ -1510,7 +1668,7 @@
         <v>50558.498384562939</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:14">
       <c r="A15" s="10" t="s">
         <v>3</v>
       </c>
@@ -1527,7 +1685,7 @@
         <v>22115.228953458598</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:14">
       <c r="A16" s="18" t="s">
         <v>46</v>
       </c>

--- a/excel/15数学函数与Row.xlsx
+++ b/excel/15数学函数与Row.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EDF4F-7190-224F-9BFF-E687DFC8C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF12FB31-F6F6-FA4E-A216-173846A1003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -371,6 +371,14 @@
   </si>
   <si>
     <t>LARGE(array,k)与SMALL相反 取最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N(value)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将值转为数字 很多人用它来写注释函数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -592,6 +600,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -600,9 +611,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -977,7 +985,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:H28"/>
+  <dimension ref="A2:H29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1045,101 +1053,109 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="3" customFormat="1" ht="14"/>
-    <row r="13" spans="1:8" s="3" customFormat="1" ht="14">
-      <c r="B13" s="3" t="s">
+    <row r="12" spans="1:8" s="3" customFormat="1" ht="14">
+      <c r="C12" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" ht="14"/>
+    <row r="14" spans="1:8" s="3" customFormat="1" ht="14">
+      <c r="B14" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1" ht="14">
-      <c r="C14" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" s="3" customFormat="1" ht="14">
       <c r="C15" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" s="3" customFormat="1" ht="14">
+      <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D16" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8" s="3" customFormat="1" ht="14"/>
-    <row r="17" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="B17" s="3" t="s">
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="2:7" s="3" customFormat="1" ht="14"/>
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="B18" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C18" s="17" t="s">
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="C19" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:7" s="3" customFormat="1">
-      <c r="C19" s="4"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" s="3" customFormat="1">
+      <c r="C20" s="4"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="B21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="14">
+      <c r="C22" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F22" s="17">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>46</v>
-      </c>
-      <c r="G21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="14"/>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" s="3" customFormat="1" ht="14"/>
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="C25" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="C25" s="21" t="s">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="C26" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="C26" s="21" t="s">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="C27" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="C27" s="21" t="s">
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="C28" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="2:7">
       <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="E29" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1350,13 +1366,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21"/>
       <c r="K1" s="14" t="s">
         <v>70</v>
       </c>
@@ -1494,13 +1510,13 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
       <c r="G6" s="8"/>
       <c r="H6" s="15" cm="1">
         <f t="array" ref="H6">INDEX($E:$E,ROW()*5-17)</f>
@@ -1609,13 +1625,13 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="10" t="s">
@@ -1686,13 +1702,13 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
@@ -1763,13 +1779,13 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="10" t="s">

--- a/excel/15数学函数与Row.xlsx
+++ b/excel/15数学函数与Row.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF12FB31-F6F6-FA4E-A216-173846A1003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55926F5D-8866-C144-9F3E-BF906B625E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F22" s="17">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>69</v>
